--- a/dks-lbo/DKS_LBO_Model.xlsx
+++ b/dks-lbo/DKS_LBO_Model.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Model" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Operating Model" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Debt Schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Returns" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sensitivity" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,9 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0&quot;x&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -192,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -303,6 +304,9 @@
     <xf numFmtId="165" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -315,6 +319,9 @@
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -797,10 +804,9 @@
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>DKS is the last major national big-box sporting goods retailer standing — Sports Authority filed for bankruptcy in 2016 and Modell’s followed in 2020. Entry at 9.0x LTM EBITDA acquires a market-share-accreting platform with a clear operational thesis: accelerating private label penetration from ~15% toward 20%+ of revenue mix drives EBITDA margins from 13% to 16.5% over the hold period. Aggressive free cash flow sweeps against the Term Loan B deleverage the business from 5.5x at entry to approximately 2.4x at exit — a transformation in earnings quality that justifies a re-rating to 10.5x on exit and delivers 3.8x MOIC and 30%+ IRR over a 5-year hold.</t>
-        </is>
+      <c r="B14" s="11">
+        <f>"DKS is the last major national big-box sporting goods retailer standing — Sports Authority filed for bankruptcy in 2016 and Modell’s followed in 2020. Entry at "&amp;TEXT(Assumptions!B7,"0.0x")&amp;" LTM EBITDA acquires a share-gaining platform: private label penetration from ~15% toward 20%+ drives EBITDA margin from "&amp;TEXT(Assumptions!B6,"0.0%")&amp;" to "&amp;TEXT(Assumptions!G38,"0.0%")&amp;". Cash sweeps cut leverage from "&amp;TEXT(Assumptions!B23,"0.0x")&amp;" at entry to "&amp;TEXT('Debt Schedule'!G23,"0.0x")&amp;" at exit; with a "&amp;TEXT(Assumptions!B45,"0.0x")&amp;" exit the deal returns "&amp;TEXT(Returns!B15,"0.0x")&amp;" MOIC / "&amp;TEXT(Returns!B17,"0.0%")&amp;" IRR over "&amp;Assumptions!B44&amp;" years."</f>
+        <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
@@ -852,10 +858,9 @@
           <t>CASH FLOW DELEVERAGING</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>$3.4B in cumulative TLB sweeps reduce net debt from $9.4B to $5.5B; compounding equity value creation through debt paydown, EBITDA growth, and exit multiple re-rating.</t>
-        </is>
+      <c r="C20" s="13">
+        <f>"$"&amp;TEXT((Assumptions!B17-'Debt Schedule'!G8)/1000,"0.0")&amp;"B of TLB paydown takes net debt from $"&amp;TEXT(Assumptions!B20/1000,"0.0")&amp;"B to $"&amp;TEXT('Debt Schedule'!G22/1000,"0.0")&amp;"B; equity value compounds through debt paydown, EBITDA growth and exit multiple re-rating."</f>
+        <v/>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -901,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:G48"/>
+  <dimension ref="A3:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -985,7 +990,7 @@
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Transaction Equity Value ($M)</t>
+          <t>Purchase of Equity ($M)</t>
         </is>
       </c>
       <c r="B10" s="20">
@@ -1015,13 +1020,24 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Refinance Existing Net Debt ($M)</t>
+        </is>
+      </c>
+      <c r="B13" s="20">
+        <f>B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Total Uses ($M)</t>
         </is>
       </c>
-      <c r="B13" s="23">
-        <f>B10+B12</f>
+      <c r="B14" s="23">
+        <f>B10+B12+B13</f>
         <v/>
       </c>
     </row>
@@ -1091,7 +1107,7 @@
         </is>
       </c>
       <c r="B21" s="20">
-        <f>B13-B20</f>
+        <f>B14-B20</f>
         <v/>
       </c>
     </row>
@@ -1124,7 +1140,7 @@
         </is>
       </c>
       <c r="B24" s="18">
-        <f>B21/B13</f>
+        <f>B21/B14</f>
         <v/>
       </c>
     </row>
@@ -1397,8 +1413,18 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="15" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Sensitivity Step — Entry / Exit Multiple (x)</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" ht="12" customHeight="1">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>Francisco Rodriguez  |  Financial Modeling Portfolio  |  github.com/Azyo1</t>
         </is>
@@ -1408,9 +1434,9 @@
   <mergeCells count="5">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A26:G26"/>
+    <mergeCell ref="B49:G49"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A43:G43"/>
-    <mergeCell ref="B48:G48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1706,9 +1732,7 @@
           <t xml:space="preserve">  Less: Interest Expense — TLB</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" s="20" t="n"/>
       <c r="C15" s="32">
         <f>'Debt Schedule'!C10</f>
         <v/>
@@ -1736,9 +1760,7 @@
           <t xml:space="preserve">  Less: Interest Expense — Revolver</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
-        <v>0</v>
-      </c>
+      <c r="B16" s="20" t="n"/>
       <c r="C16" s="32">
         <f>'Debt Schedule'!C17</f>
         <v/>
@@ -1766,9 +1788,7 @@
           <t>Total Interest Expense</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n">
-        <v>0</v>
-      </c>
+      <c r="B17" s="20" t="n"/>
       <c r="C17" s="20">
         <f>C15+C16</f>
         <v/>
@@ -2118,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2206,23 +2226,23 @@
         </is>
       </c>
       <c r="C6" s="20">
-        <f>-'Assumptions'!B17*'Assumptions'!B30</f>
+        <f>-MIN('Assumptions'!B17*'Assumptions'!B30,C5)</f>
         <v/>
       </c>
       <c r="D6" s="20">
-        <f>-'Assumptions'!B17*'Assumptions'!B30</f>
+        <f>-MIN('Assumptions'!B17*'Assumptions'!B30,D5)</f>
         <v/>
       </c>
       <c r="E6" s="20">
-        <f>-'Assumptions'!B17*'Assumptions'!B30</f>
+        <f>-MIN('Assumptions'!B17*'Assumptions'!B30,E5)</f>
         <v/>
       </c>
       <c r="F6" s="20">
-        <f>-'Assumptions'!B17*'Assumptions'!B30</f>
+        <f>-MIN('Assumptions'!B17*'Assumptions'!B30,F5)</f>
         <v/>
       </c>
       <c r="G6" s="20">
-        <f>-'Assumptions'!B17*'Assumptions'!B30</f>
+        <f>-MIN('Assumptions'!B17*'Assumptions'!B30,G5)</f>
         <v/>
       </c>
     </row>
@@ -2233,23 +2253,23 @@
         </is>
       </c>
       <c r="C7" s="20">
-        <f>-MAX(0,'Operating Model'!C32)</f>
+        <f>-MIN(MAX(0,'Operating Model'!C32),C5+C6)</f>
         <v/>
       </c>
       <c r="D7" s="20">
-        <f>-MAX(0,'Operating Model'!D32)</f>
+        <f>-MIN(MAX(0,'Operating Model'!D32),D5+D6)</f>
         <v/>
       </c>
       <c r="E7" s="20">
-        <f>-MAX(0,'Operating Model'!E32)</f>
+        <f>-MIN(MAX(0,'Operating Model'!E32),E5+E6)</f>
         <v/>
       </c>
       <c r="F7" s="20">
-        <f>-MAX(0,'Operating Model'!F32)</f>
+        <f>-MIN(MAX(0,'Operating Model'!F32),F5+F6)</f>
         <v/>
       </c>
       <c r="G7" s="20">
-        <f>-MAX(0,'Operating Model'!G32)</f>
+        <f>-MIN(MAX(0,'Operating Model'!G32),G5+G6)</f>
         <v/>
       </c>
     </row>
@@ -2260,23 +2280,23 @@
         </is>
       </c>
       <c r="C8" s="23">
-        <f>MAX(0,C5+C6+C7)</f>
+        <f>C5+C6+C7</f>
         <v/>
       </c>
       <c r="D8" s="23">
-        <f>MAX(0,D5+D6+D7)</f>
+        <f>D5+D6+D7</f>
         <v/>
       </c>
       <c r="E8" s="23">
-        <f>MAX(0,E5+E6+E7)</f>
+        <f>E5+E6+E7</f>
         <v/>
       </c>
       <c r="F8" s="23">
-        <f>MAX(0,F5+F6+F7)</f>
+        <f>F5+F6+F7</f>
         <v/>
       </c>
       <c r="G8" s="23">
-        <f>MAX(0,G5+G6+G7)</f>
+        <f>G5+G6+G7</f>
         <v/>
       </c>
     </row>
@@ -2538,29 +2558,29 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Total Net Debt at Exit</t>
-        </is>
-      </c>
-      <c r="C22" s="20">
-        <f>C21</f>
-        <v/>
-      </c>
-      <c r="D22" s="20">
-        <f>D21</f>
-        <v/>
-      </c>
-      <c r="E22" s="20">
-        <f>E21</f>
-        <v/>
-      </c>
-      <c r="F22" s="20">
-        <f>F21</f>
-        <v/>
-      </c>
-      <c r="G22" s="20">
-        <f>G21</f>
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net Debt (Total Debt − Cash)</t>
+        </is>
+      </c>
+      <c r="C22" s="23">
+        <f>C21-C28</f>
+        <v/>
+      </c>
+      <c r="D22" s="23">
+        <f>D21-D28</f>
+        <v/>
+      </c>
+      <c r="E22" s="23">
+        <f>E21-E28</f>
+        <v/>
+      </c>
+      <c r="F22" s="23">
+        <f>F21-F28</f>
+        <v/>
+      </c>
+      <c r="G22" s="23">
+        <f>G21-G28</f>
         <v/>
       </c>
     </row>
@@ -2591,19 +2611,108 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>CASH  (excess levered FCF once TLB is repaid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Beginning Cash</t>
+        </is>
+      </c>
+      <c r="C26" s="20">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D26" s="20">
+        <f>C28</f>
+        <v/>
+      </c>
+      <c r="E26" s="20">
+        <f>D28</f>
+        <v/>
+      </c>
+      <c r="F26" s="20">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="G26" s="20">
+        <f>F28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Plus: Levered FCF not used for debt paydown</t>
+        </is>
+      </c>
+      <c r="C27" s="20">
+        <f>MAX(0,'Operating Model'!C32)+C7</f>
+        <v/>
+      </c>
+      <c r="D27" s="20">
+        <f>MAX(0,'Operating Model'!D32)+D7</f>
+        <v/>
+      </c>
+      <c r="E27" s="20">
+        <f>MAX(0,'Operating Model'!E32)+E7</f>
+        <v/>
+      </c>
+      <c r="F27" s="20">
+        <f>MAX(0,'Operating Model'!F32)+F7</f>
+        <v/>
+      </c>
+      <c r="G27" s="20">
+        <f>MAX(0,'Operating Model'!G32)+G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ending Cash</t>
+        </is>
+      </c>
+      <c r="C28" s="23">
+        <f>C26+C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="23">
+        <f>D26+D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="23">
+        <f>E26+E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="23">
+        <f>F26+F27</f>
+        <v/>
+      </c>
+      <c r="G28" s="23">
+        <f>G26+G27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="12" customHeight="1">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Francisco Rodriguez  |  Financial Modeling Portfolio  |  github.com/Azyo1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="B25:G25"/>
+  <mergeCells count="5">
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2677,7 +2786,7 @@
         </is>
       </c>
       <c r="B7" s="32">
-        <f>'Debt Schedule'!G8</f>
+        <f>'Debt Schedule'!G22</f>
         <v/>
       </c>
     </row>
@@ -2800,7 +2909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2832,171 +2941,161 @@
           <t>Entry \ Exit</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
-        <is>
-          <t>7.0x</t>
-        </is>
-      </c>
-      <c r="C4" s="28" t="inlineStr">
-        <is>
-          <t>8.0x</t>
-        </is>
-      </c>
-      <c r="D4" s="28" t="inlineStr">
-        <is>
-          <t>9.0x</t>
-        </is>
-      </c>
-      <c r="E4" s="28" t="inlineStr">
-        <is>
-          <t>10.0x</t>
-        </is>
-      </c>
-      <c r="F4" s="28" t="inlineStr">
-        <is>
-          <t>11.0x</t>
-        </is>
+      <c r="B4" s="40">
+        <f>'Assumptions'!$B$45+(-2)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="C4" s="40">
+        <f>'Assumptions'!$B$45+(-1)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="D4" s="40">
+        <f>'Assumptions'!$B$45+(0)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="E4" s="40">
+        <f>'Assumptions'!$B$45+(1)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="F4" s="40">
+        <f>'Assumptions'!$B$45+(2)*'Assumptions'!$B$47</f>
+        <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>7.0x</t>
-        </is>
-      </c>
-      <c r="B5" s="40">
-        <f>IFERROR(((7.0*'Operating Model'!G8-'Debt Schedule'!G8-7.0*'Operating Model'!G8*'Assumptions'!B46)/(7.0*'Assumptions'!B5-'Assumptions'!B9-7.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="C5" s="40">
-        <f>IFERROR(((8.0*'Operating Model'!G8-'Debt Schedule'!G8-8.0*'Operating Model'!G8*'Assumptions'!B46)/(7.0*'Assumptions'!B5-'Assumptions'!B9-7.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="D5" s="40">
-        <f>IFERROR(((9.0*'Operating Model'!G8-'Debt Schedule'!G8-9.0*'Operating Model'!G8*'Assumptions'!B46)/(7.0*'Assumptions'!B5-'Assumptions'!B9-7.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="E5" s="40">
-        <f>IFERROR(((10.0*'Operating Model'!G8-'Debt Schedule'!G8-10.0*'Operating Model'!G8*'Assumptions'!B46)/(7.0*'Assumptions'!B5-'Assumptions'!B9-7.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="F5" s="40">
-        <f>IFERROR(((11.0*'Operating Model'!G8-'Debt Schedule'!G8-11.0*'Operating Model'!G8*'Assumptions'!B46)/(7.0*'Assumptions'!B5-'Assumptions'!B9-7.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
+      <c r="A5" s="40">
+        <f>'Assumptions'!$B$7+(-2)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="B5" s="41">
+        <f>IFERROR(((B$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A5*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="C5" s="41">
+        <f>IFERROR(((C$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A5*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D5" s="41">
+        <f>IFERROR(((D$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A5*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E5" s="41">
+        <f>IFERROR(((E$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A5*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F5" s="41">
+        <f>IFERROR(((F$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A5*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
-        <is>
-          <t>8.0x</t>
-        </is>
-      </c>
-      <c r="B6" s="40">
-        <f>IFERROR(((7.0*'Operating Model'!G8-'Debt Schedule'!G8-7.0*'Operating Model'!G8*'Assumptions'!B46)/(8.0*'Assumptions'!B5-'Assumptions'!B9-8.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="C6" s="40">
-        <f>IFERROR(((8.0*'Operating Model'!G8-'Debt Schedule'!G8-8.0*'Operating Model'!G8*'Assumptions'!B46)/(8.0*'Assumptions'!B5-'Assumptions'!B9-8.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="D6" s="40">
-        <f>IFERROR(((9.0*'Operating Model'!G8-'Debt Schedule'!G8-9.0*'Operating Model'!G8*'Assumptions'!B46)/(8.0*'Assumptions'!B5-'Assumptions'!B9-8.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="E6" s="40">
-        <f>IFERROR(((10.0*'Operating Model'!G8-'Debt Schedule'!G8-10.0*'Operating Model'!G8*'Assumptions'!B46)/(8.0*'Assumptions'!B5-'Assumptions'!B9-8.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="F6" s="40">
-        <f>IFERROR(((11.0*'Operating Model'!G8-'Debt Schedule'!G8-11.0*'Operating Model'!G8*'Assumptions'!B46)/(8.0*'Assumptions'!B5-'Assumptions'!B9-8.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
+      <c r="A6" s="40">
+        <f>'Assumptions'!$B$7+(-1)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="B6" s="41">
+        <f>IFERROR(((B$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A6*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="C6" s="41">
+        <f>IFERROR(((C$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A6*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D6" s="41">
+        <f>IFERROR(((D$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A6*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E6" s="41">
+        <f>IFERROR(((E$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A6*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F6" s="41">
+        <f>IFERROR(((F$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A6*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>9.0x</t>
-        </is>
-      </c>
-      <c r="B7" s="40">
-        <f>IFERROR(((7.0*'Operating Model'!G8-'Debt Schedule'!G8-7.0*'Operating Model'!G8*'Assumptions'!B46)/(9.0*'Assumptions'!B5-'Assumptions'!B9-9.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="C7" s="40">
-        <f>IFERROR(((8.0*'Operating Model'!G8-'Debt Schedule'!G8-8.0*'Operating Model'!G8*'Assumptions'!B46)/(9.0*'Assumptions'!B5-'Assumptions'!B9-9.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="D7" s="41">
-        <f>IFERROR(((9.0*'Operating Model'!G8-'Debt Schedule'!G8-9.0*'Operating Model'!G8*'Assumptions'!B46)/(9.0*'Assumptions'!B5-'Assumptions'!B9-9.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="E7" s="40">
-        <f>IFERROR(((10.0*'Operating Model'!G8-'Debt Schedule'!G8-10.0*'Operating Model'!G8*'Assumptions'!B46)/(9.0*'Assumptions'!B5-'Assumptions'!B9-9.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="F7" s="40">
-        <f>IFERROR(((11.0*'Operating Model'!G8-'Debt Schedule'!G8-11.0*'Operating Model'!G8*'Assumptions'!B46)/(9.0*'Assumptions'!B5-'Assumptions'!B9-9.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
+      <c r="A7" s="40">
+        <f>'Assumptions'!$B$7+(0)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="B7" s="41">
+        <f>IFERROR(((B$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A7*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="C7" s="41">
+        <f>IFERROR(((C$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A7*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D7" s="42">
+        <f>IFERROR(((D$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A7*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E7" s="41">
+        <f>IFERROR(((E$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A7*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F7" s="41">
+        <f>IFERROR(((F$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A7*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>10.0x</t>
-        </is>
-      </c>
-      <c r="B8" s="40">
-        <f>IFERROR(((7.0*'Operating Model'!G8-'Debt Schedule'!G8-7.0*'Operating Model'!G8*'Assumptions'!B46)/(10.0*'Assumptions'!B5-'Assumptions'!B9-10.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="C8" s="40">
-        <f>IFERROR(((8.0*'Operating Model'!G8-'Debt Schedule'!G8-8.0*'Operating Model'!G8*'Assumptions'!B46)/(10.0*'Assumptions'!B5-'Assumptions'!B9-10.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="D8" s="40">
-        <f>IFERROR(((9.0*'Operating Model'!G8-'Debt Schedule'!G8-9.0*'Operating Model'!G8*'Assumptions'!B46)/(10.0*'Assumptions'!B5-'Assumptions'!B9-10.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="E8" s="40">
-        <f>IFERROR(((10.0*'Operating Model'!G8-'Debt Schedule'!G8-10.0*'Operating Model'!G8*'Assumptions'!B46)/(10.0*'Assumptions'!B5-'Assumptions'!B9-10.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="F8" s="40">
-        <f>IFERROR(((11.0*'Operating Model'!G8-'Debt Schedule'!G8-11.0*'Operating Model'!G8*'Assumptions'!B46)/(10.0*'Assumptions'!B5-'Assumptions'!B9-10.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
+      <c r="A8" s="40">
+        <f>'Assumptions'!$B$7+(1)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="B8" s="41">
+        <f>IFERROR(((B$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A8*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="C8" s="41">
+        <f>IFERROR(((C$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A8*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D8" s="41">
+        <f>IFERROR(((D$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A8*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E8" s="41">
+        <f>IFERROR(((E$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A8*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F8" s="41">
+        <f>IFERROR(((F$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A8*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>11.0x</t>
-        </is>
-      </c>
-      <c r="B9" s="40">
-        <f>IFERROR(((7.0*'Operating Model'!G8-'Debt Schedule'!G8-7.0*'Operating Model'!G8*'Assumptions'!B46)/(11.0*'Assumptions'!B5-'Assumptions'!B9-11.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="C9" s="40">
-        <f>IFERROR(((8.0*'Operating Model'!G8-'Debt Schedule'!G8-8.0*'Operating Model'!G8*'Assumptions'!B46)/(11.0*'Assumptions'!B5-'Assumptions'!B9-11.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="D9" s="40">
-        <f>IFERROR(((9.0*'Operating Model'!G8-'Debt Schedule'!G8-9.0*'Operating Model'!G8*'Assumptions'!B46)/(11.0*'Assumptions'!B5-'Assumptions'!B9-11.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="E9" s="40">
-        <f>IFERROR(((10.0*'Operating Model'!G8-'Debt Schedule'!G8-10.0*'Operating Model'!G8*'Assumptions'!B46)/(11.0*'Assumptions'!B5-'Assumptions'!B9-11.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
-        <v/>
-      </c>
-      <c r="F9" s="40">
-        <f>IFERROR(((11.0*'Operating Model'!G8-'Debt Schedule'!G8-11.0*'Operating Model'!G8*'Assumptions'!B46)/(11.0*'Assumptions'!B5-'Assumptions'!B9-11.0*'Assumptions'!B5*'Assumptions'!B11))^(1/'Assumptions'!B44)-1,"N/A")</f>
+      <c r="A9" s="40">
+        <f>'Assumptions'!$B$7+(2)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="B9" s="41">
+        <f>IFERROR(((B$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A9*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="C9" s="41">
+        <f>IFERROR(((C$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A9*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D9" s="41">
+        <f>IFERROR(((D$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A9*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E9" s="41">
+        <f>IFERROR(((E$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A9*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F9" s="41">
+        <f>IFERROR(((F$4*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A9*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20))^(1/'Assumptions'!B44)-1,"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="42" t="inlineStr">
-        <is>
-          <t>Rows = Entry EV/EBITDA Multiple | Columns = Exit EV/EBITDA Multiple</t>
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Rows = Entry EV/EBITDA | Columns = Exit EV/EBITDA | Boxed centre = base case (must equal Returns tab)</t>
         </is>
       </c>
     </row>
@@ -3013,176 +3112,177 @@
           <t>Entry \ Exit</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
-        <is>
-          <t>7.0x</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="inlineStr">
-        <is>
-          <t>8.0x</t>
-        </is>
-      </c>
-      <c r="D14" s="28" t="inlineStr">
-        <is>
-          <t>9.0x</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="inlineStr">
-        <is>
-          <t>10.0x</t>
-        </is>
-      </c>
-      <c r="F14" s="28" t="inlineStr">
-        <is>
-          <t>11.0x</t>
-        </is>
+      <c r="B14" s="40">
+        <f>'Assumptions'!$B$45+(-2)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="C14" s="40">
+        <f>'Assumptions'!$B$45+(-1)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="D14" s="40">
+        <f>'Assumptions'!$B$45+(0)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="E14" s="40">
+        <f>'Assumptions'!$B$45+(1)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="F14" s="40">
+        <f>'Assumptions'!$B$45+(2)*'Assumptions'!$B$47</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>7.0x</t>
-        </is>
-      </c>
-      <c r="B15" s="43">
-        <f>IFERROR((7.0*'Operating Model'!G8-'Debt Schedule'!G8-7.0*'Operating Model'!G8*'Assumptions'!B46)/(7.0*'Assumptions'!B5-'Assumptions'!B9-7.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="C15" s="43">
-        <f>IFERROR((8.0*'Operating Model'!G8-'Debt Schedule'!G8-8.0*'Operating Model'!G8*'Assumptions'!B46)/(7.0*'Assumptions'!B5-'Assumptions'!B9-7.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="D15" s="43">
-        <f>IFERROR((9.0*'Operating Model'!G8-'Debt Schedule'!G8-9.0*'Operating Model'!G8*'Assumptions'!B46)/(7.0*'Assumptions'!B5-'Assumptions'!B9-7.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="E15" s="43">
-        <f>IFERROR((10.0*'Operating Model'!G8-'Debt Schedule'!G8-10.0*'Operating Model'!G8*'Assumptions'!B46)/(7.0*'Assumptions'!B5-'Assumptions'!B9-7.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="F15" s="43">
-        <f>IFERROR((11.0*'Operating Model'!G8-'Debt Schedule'!G8-11.0*'Operating Model'!G8*'Assumptions'!B46)/(7.0*'Assumptions'!B5-'Assumptions'!B9-7.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
+      <c r="A15" s="40">
+        <f>'Assumptions'!$B$7+(-2)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="B15" s="44">
+        <f>IFERROR((B$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A15*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="C15" s="44">
+        <f>IFERROR((C$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A15*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="D15" s="44">
+        <f>IFERROR((D$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A15*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="E15" s="44">
+        <f>IFERROR((E$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A15*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="F15" s="44">
+        <f>IFERROR((F$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A15*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>8.0x</t>
-        </is>
-      </c>
-      <c r="B16" s="43">
-        <f>IFERROR((7.0*'Operating Model'!G8-'Debt Schedule'!G8-7.0*'Operating Model'!G8*'Assumptions'!B46)/(8.0*'Assumptions'!B5-'Assumptions'!B9-8.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="C16" s="43">
-        <f>IFERROR((8.0*'Operating Model'!G8-'Debt Schedule'!G8-8.0*'Operating Model'!G8*'Assumptions'!B46)/(8.0*'Assumptions'!B5-'Assumptions'!B9-8.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="D16" s="43">
-        <f>IFERROR((9.0*'Operating Model'!G8-'Debt Schedule'!G8-9.0*'Operating Model'!G8*'Assumptions'!B46)/(8.0*'Assumptions'!B5-'Assumptions'!B9-8.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="E16" s="43">
-        <f>IFERROR((10.0*'Operating Model'!G8-'Debt Schedule'!G8-10.0*'Operating Model'!G8*'Assumptions'!B46)/(8.0*'Assumptions'!B5-'Assumptions'!B9-8.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="F16" s="43">
-        <f>IFERROR((11.0*'Operating Model'!G8-'Debt Schedule'!G8-11.0*'Operating Model'!G8*'Assumptions'!B46)/(8.0*'Assumptions'!B5-'Assumptions'!B9-8.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
+      <c r="A16" s="40">
+        <f>'Assumptions'!$B$7+(-1)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="B16" s="44">
+        <f>IFERROR((B$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A16*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="C16" s="44">
+        <f>IFERROR((C$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A16*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="D16" s="44">
+        <f>IFERROR((D$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A16*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="E16" s="44">
+        <f>IFERROR((E$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A16*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="F16" s="44">
+        <f>IFERROR((F$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A16*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>9.0x</t>
-        </is>
-      </c>
-      <c r="B17" s="43">
-        <f>IFERROR((7.0*'Operating Model'!G8-'Debt Schedule'!G8-7.0*'Operating Model'!G8*'Assumptions'!B46)/(9.0*'Assumptions'!B5-'Assumptions'!B9-9.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="C17" s="43">
-        <f>IFERROR((8.0*'Operating Model'!G8-'Debt Schedule'!G8-8.0*'Operating Model'!G8*'Assumptions'!B46)/(9.0*'Assumptions'!B5-'Assumptions'!B9-9.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="D17" s="44">
-        <f>IFERROR((9.0*'Operating Model'!G8-'Debt Schedule'!G8-9.0*'Operating Model'!G8*'Assumptions'!B46)/(9.0*'Assumptions'!B5-'Assumptions'!B9-9.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="E17" s="43">
-        <f>IFERROR((10.0*'Operating Model'!G8-'Debt Schedule'!G8-10.0*'Operating Model'!G8*'Assumptions'!B46)/(9.0*'Assumptions'!B5-'Assumptions'!B9-9.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="F17" s="43">
-        <f>IFERROR((11.0*'Operating Model'!G8-'Debt Schedule'!G8-11.0*'Operating Model'!G8*'Assumptions'!B46)/(9.0*'Assumptions'!B5-'Assumptions'!B9-9.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
+      <c r="A17" s="40">
+        <f>'Assumptions'!$B$7+(0)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="B17" s="44">
+        <f>IFERROR((B$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A17*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="C17" s="44">
+        <f>IFERROR((C$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A17*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="D17" s="45">
+        <f>IFERROR((D$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A17*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="E17" s="44">
+        <f>IFERROR((E$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A17*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="F17" s="44">
+        <f>IFERROR((F$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A17*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>10.0x</t>
-        </is>
-      </c>
-      <c r="B18" s="43">
-        <f>IFERROR((7.0*'Operating Model'!G8-'Debt Schedule'!G8-7.0*'Operating Model'!G8*'Assumptions'!B46)/(10.0*'Assumptions'!B5-'Assumptions'!B9-10.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="C18" s="43">
-        <f>IFERROR((8.0*'Operating Model'!G8-'Debt Schedule'!G8-8.0*'Operating Model'!G8*'Assumptions'!B46)/(10.0*'Assumptions'!B5-'Assumptions'!B9-10.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="D18" s="43">
-        <f>IFERROR((9.0*'Operating Model'!G8-'Debt Schedule'!G8-9.0*'Operating Model'!G8*'Assumptions'!B46)/(10.0*'Assumptions'!B5-'Assumptions'!B9-10.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="E18" s="43">
-        <f>IFERROR((10.0*'Operating Model'!G8-'Debt Schedule'!G8-10.0*'Operating Model'!G8*'Assumptions'!B46)/(10.0*'Assumptions'!B5-'Assumptions'!B9-10.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="F18" s="43">
-        <f>IFERROR((11.0*'Operating Model'!G8-'Debt Schedule'!G8-11.0*'Operating Model'!G8*'Assumptions'!B46)/(10.0*'Assumptions'!B5-'Assumptions'!B9-10.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
+      <c r="A18" s="40">
+        <f>'Assumptions'!$B$7+(1)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="B18" s="44">
+        <f>IFERROR((B$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A18*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="C18" s="44">
+        <f>IFERROR((C$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A18*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="D18" s="44">
+        <f>IFERROR((D$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A18*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="E18" s="44">
+        <f>IFERROR((E$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A18*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="F18" s="44">
+        <f>IFERROR((F$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A18*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>11.0x</t>
-        </is>
-      </c>
-      <c r="B19" s="43">
-        <f>IFERROR((7.0*'Operating Model'!G8-'Debt Schedule'!G8-7.0*'Operating Model'!G8*'Assumptions'!B46)/(11.0*'Assumptions'!B5-'Assumptions'!B9-11.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="C19" s="43">
-        <f>IFERROR((8.0*'Operating Model'!G8-'Debt Schedule'!G8-8.0*'Operating Model'!G8*'Assumptions'!B46)/(11.0*'Assumptions'!B5-'Assumptions'!B9-11.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="D19" s="43">
-        <f>IFERROR((9.0*'Operating Model'!G8-'Debt Schedule'!G8-9.0*'Operating Model'!G8*'Assumptions'!B46)/(11.0*'Assumptions'!B5-'Assumptions'!B9-11.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="E19" s="43">
-        <f>IFERROR((10.0*'Operating Model'!G8-'Debt Schedule'!G8-10.0*'Operating Model'!G8*'Assumptions'!B46)/(11.0*'Assumptions'!B5-'Assumptions'!B9-11.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
-        <v/>
-      </c>
-      <c r="F19" s="43">
-        <f>IFERROR((11.0*'Operating Model'!G8-'Debt Schedule'!G8-11.0*'Operating Model'!G8*'Assumptions'!B46)/(11.0*'Assumptions'!B5-'Assumptions'!B9-11.0*'Assumptions'!B5*'Assumptions'!B11),"N/A")</f>
+      <c r="A19" s="40">
+        <f>'Assumptions'!$B$7+(2)*'Assumptions'!$B$47</f>
+        <v/>
+      </c>
+      <c r="B19" s="44">
+        <f>IFERROR((B$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A19*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="C19" s="44">
+        <f>IFERROR((C$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A19*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="D19" s="44">
+        <f>IFERROR((D$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A19*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="E19" s="44">
+        <f>IFERROR((E$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A19*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
+        <v/>
+      </c>
+      <c r="F19" s="44">
+        <f>IFERROR((F$14*'Operating Model'!$G$8*(1-'Assumptions'!$B$46)-'Debt Schedule'!$G$22)/($A19*'Assumptions'!$B$5*(1+'Assumptions'!$B$11)-'Assumptions'!$B$20),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>Rows = Entry EV/EBITDA Multiple | Columns = Exit EV/EBITDA Multiple</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="15" t="inlineStr">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>Rows = Entry EV/EBITDA | Columns = Exit EV/EBITDA | Boxed centre = base case (must equal Returns tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>Check: centre IRR − Returns!B17</t>
+        </is>
+      </c>
+      <c r="B24" s="46">
+        <f>ROUND(D7-Returns!B17,6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="12" customHeight="1">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>Francisco Rodriguez  |  Financial Modeling Portfolio  |  github.com/Azyo1</t>
         </is>
@@ -3192,7 +3292,7 @@
   <mergeCells count="3">
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B26:G26"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:F9">
     <cfRule type="colorScale" priority="1">
